--- a/tabtools/qa/output/regtab_ext_test2.xlsx
+++ b/tabtools/qa/output/regtab_ext_test2.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="640" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="705" uniqueCount="46">
   <si>
     <t>Test 2: Mixed Model</t>
   </si>
@@ -157,1961 +157,3193 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="2883">
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
+  <fonts count="3175">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -12339,7 +13571,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2173">
+  <borders count="2393">
     <border>
       <left/>
       <right/>
@@ -27251,11 +28483,1521 @@
       <bottom style="thin"/>
       <diagonal style="none"/>
     </border>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2173">
+  <cellXfs count="2393">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
@@ -35792,6 +38534,871 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="2882" fillId="0" borderId="2172" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2173" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2174" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2175" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2176" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2177" xfId="0"/>
+    <xf numFmtId="0" fontId="2883" fillId="0" borderId="2178" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2884" fillId="0" borderId="2179" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2885" fillId="0" borderId="2180" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2886" fillId="0" borderId="2181" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2887" fillId="0" borderId="2182" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2888" fillId="0" borderId="2183" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2890" fillId="0" borderId="2184" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2892" fillId="0" borderId="2185" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2894" fillId="0" borderId="2186" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2895" fillId="0" borderId="2187" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2896" fillId="0" borderId="2188" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2897" fillId="0" borderId="2189" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2898" fillId="0" borderId="2190" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2899" fillId="0" borderId="2191" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2900" fillId="0" borderId="2192" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2901" fillId="0" borderId="2193" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2902" fillId="0" borderId="2194" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2903" fillId="0" borderId="2195" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2904" fillId="0" borderId="2196" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2905" fillId="0" borderId="2197" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2906" fillId="0" borderId="2198" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2907" fillId="0" borderId="2199" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2908" fillId="0" borderId="2200" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2909" fillId="0" borderId="2201" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2910" fillId="0" borderId="2202" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2911" fillId="0" borderId="2203" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2912" fillId="0" borderId="2204" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2913" fillId="0" borderId="2205" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2914" fillId="0" borderId="2206" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2915" fillId="0" borderId="2207" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2916" fillId="0" borderId="2208" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2917" fillId="0" borderId="2209" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2918" fillId="0" borderId="2210" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2919" fillId="0" borderId="2211" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2921" fillId="0" borderId="2212" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2923" fillId="0" borderId="2213" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2925" fillId="0" borderId="2214" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2927" fillId="0" borderId="2215" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2929" fillId="0" borderId="2216" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2930" fillId="0" borderId="2217" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2931" fillId="0" borderId="2218" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2932" fillId="0" borderId="2219" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2933" fillId="0" borderId="2220" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2934" fillId="0" borderId="2221" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2935" fillId="0" borderId="2222" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2936" fillId="0" borderId="2223" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2937" fillId="0" borderId="2224" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2938" fillId="0" borderId="2225" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2939" fillId="0" borderId="2226" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2940" fillId="0" borderId="2227" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2941" fillId="0" borderId="2228" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2942" fillId="0" borderId="2229" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2944" fillId="0" borderId="2230" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2946" fillId="0" borderId="2231" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2948" fillId="0" borderId="2232" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2950" fillId="0" borderId="2233" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2951" fillId="0" borderId="2234" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2952" fillId="0" borderId="2235" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2953" fillId="0" borderId="2236" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2954" fillId="0" borderId="2237" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2955" fillId="0" borderId="2238" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2956" fillId="0" borderId="2239" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2957" fillId="0" borderId="2240" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2958" fillId="0" borderId="2241" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2959" fillId="0" borderId="2242" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2960" fillId="0" borderId="2243" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2961" fillId="0" borderId="2244" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2962" fillId="0" borderId="2245" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2963" fillId="0" borderId="2246" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2964" fillId="0" borderId="2247" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2965" fillId="0" borderId="2248" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2966" fillId="0" borderId="2249" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2967" fillId="0" borderId="2250" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2968" fillId="0" borderId="2251" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2969" fillId="0" borderId="2252" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2970" fillId="0" borderId="2253" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2971" fillId="0" borderId="2254" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2972" fillId="0" borderId="2255" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2973" fillId="0" borderId="2256" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2974" fillId="0" borderId="2257" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2975" fillId="0" borderId="2258" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2976" fillId="0" borderId="2259" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2977" fillId="0" borderId="2260" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2978" fillId="0" borderId="2261" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2979" fillId="0" borderId="2262" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2980" fillId="0" borderId="2263" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2981" fillId="0" borderId="2264" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2982" fillId="0" borderId="2265" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2983" fillId="0" borderId="2266" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2984" fillId="0" borderId="2267" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2985" fillId="0" borderId="2268" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2986" fillId="0" borderId="2269" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2987" fillId="0" borderId="2270" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2988" fillId="0" borderId="2271" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2989" fillId="0" borderId="2272" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2990" fillId="0" borderId="2273" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2991" fillId="0" borderId="2274" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2992" fillId="0" borderId="2275" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2993" fillId="0" borderId="2276" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2994" fillId="0" borderId="2277" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2995" fillId="0" borderId="2278" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2996" fillId="0" borderId="2279" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2997" fillId="0" borderId="2280" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2998" fillId="0" borderId="2281" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2999" fillId="0" borderId="2282" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3000" fillId="0" borderId="2283" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3001" fillId="0" borderId="2284" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3002" fillId="0" borderId="2285" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3003" fillId="0" borderId="2286" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3004" fillId="0" borderId="2287" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3005" fillId="0" borderId="2288" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3006" fillId="0" borderId="2289" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3007" fillId="0" borderId="2290" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3008" fillId="0" borderId="2291" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3009" fillId="0" borderId="2292" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3010" fillId="0" borderId="2293" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3011" fillId="0" borderId="2294" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3012" fillId="0" borderId="2295" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3013" fillId="0" borderId="2296" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3014" fillId="0" borderId="2297" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3015" fillId="0" borderId="2298" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3016" fillId="0" borderId="2299" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3017" fillId="0" borderId="2300" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3018" fillId="0" borderId="2301" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3019" fillId="0" borderId="2302" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3020" fillId="0" borderId="2303" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3021" fillId="0" borderId="2304" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3022" fillId="0" borderId="2305" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3023" fillId="0" borderId="2306" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3024" fillId="0" borderId="2307" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3025" fillId="0" borderId="2308" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3026" fillId="0" borderId="2309" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3027" fillId="0" borderId="2310" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3028" fillId="0" borderId="2311" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3029" fillId="0" borderId="2312" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3030" fillId="0" borderId="2313" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3031" fillId="0" borderId="2314" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3032" fillId="0" borderId="2315" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3033" fillId="0" borderId="2316" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3034" fillId="0" borderId="2317" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3035" fillId="0" borderId="2318" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3036" fillId="0" borderId="2319" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3037" fillId="0" borderId="2320" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3038" fillId="0" borderId="2321" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3039" fillId="0" borderId="2322" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3040" fillId="0" borderId="2323" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3041" fillId="0" borderId="2324" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3042" fillId="0" borderId="2325" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3043" fillId="0" borderId="2326" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3044" fillId="0" borderId="2327" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3046" fillId="0" borderId="2328" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3048" fillId="0" borderId="2329" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3050" fillId="0" borderId="2330" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3052" fillId="0" borderId="2331" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3054" fillId="0" borderId="2332" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3056" fillId="0" borderId="2333" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3058" fillId="0" borderId="2334" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3060" fillId="0" borderId="2335" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3062" fillId="0" borderId="2336" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3064" fillId="0" borderId="2337" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3066" fillId="0" borderId="2338" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3068" fillId="0" borderId="2339" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3070" fillId="0" borderId="2340" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3072" fillId="0" borderId="2341" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3074" fillId="0" borderId="2342" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3076" fillId="0" borderId="2343" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3078" fillId="0" borderId="2344" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3080" fillId="0" borderId="2345" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3082" fillId="0" borderId="2346" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3084" fillId="0" borderId="2347" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3086" fillId="0" borderId="2348" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3088" fillId="0" borderId="2349" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3090" fillId="0" borderId="2350" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3092" fillId="0" borderId="2351" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3094" fillId="0" borderId="2352" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3096" fillId="0" borderId="2353" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3098" fillId="0" borderId="2354" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3100" fillId="0" borderId="2355" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3102" fillId="0" borderId="2356" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3104" fillId="0" borderId="2357" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3106" fillId="0" borderId="2358" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3108" fillId="0" borderId="2359" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3110" fillId="0" borderId="2360" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3112" fillId="0" borderId="2361" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3114" fillId="0" borderId="2362" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3116" fillId="0" borderId="2363" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3118" fillId="0" borderId="2364" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3120" fillId="0" borderId="2365" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3122" fillId="0" borderId="2366" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3124" fillId="0" borderId="2367" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3126" fillId="0" borderId="2368" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3128" fillId="0" borderId="2369" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3130" fillId="0" borderId="2370" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3132" fillId="0" borderId="2371" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3134" fillId="0" borderId="2372" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3136" fillId="0" borderId="2373" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3138" fillId="0" borderId="2374" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3140" fillId="0" borderId="2375" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3142" fillId="0" borderId="2376" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3144" fillId="0" borderId="2377" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3146" fillId="0" borderId="2378" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3148" fillId="0" borderId="2379" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3150" fillId="0" borderId="2380" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3152" fillId="0" borderId="2381" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3154" fillId="0" borderId="2382" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3156" fillId="0" borderId="2383" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3158" fillId="0" borderId="2384" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3160" fillId="0" borderId="2385" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3162" fillId="0" borderId="2386" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3164" fillId="0" borderId="2387" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3166" fillId="0" borderId="2388" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3168" fillId="0" borderId="2389" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3170" fillId="0" borderId="2390" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3172" fillId="0" borderId="2391" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3174" fillId="0" borderId="2392" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -35807,230 +39414,230 @@
   <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="27.7109375" style="1954" customWidth="true"/>
-    <col min="3" max="3" width="5.11328125" style="1955" customWidth="true"/>
-    <col min="4" max="4" width="11.11328125" style="1956" customWidth="true"/>
-    <col min="5" max="5" width="7.7109375" style="1957" customWidth="true"/>
+    <col min="2" max="2" width="27.7109375" style="2174" customWidth="true"/>
+    <col min="3" max="3" width="5.11328125" style="2175" customWidth="true"/>
+    <col min="4" max="4" width="11.11328125" style="2176" customWidth="true"/>
+    <col min="5" max="5" width="7.7109375" style="2177" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" s="1953" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="2108" t="s">
+    <row r="1" s="2173" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="2328" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2109" t="s">
+      <c r="B1" s="2329" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2110" t="s">
+      <c r="C1" s="2330" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2111" t="s">
+      <c r="D1" s="2331" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="2112" t="s">
+      <c r="E1" s="2332" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2113" t="s">
+      <c r="A2" s="2333" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2114" t="s">
+      <c r="B2" s="2334" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2115" t="s">
+      <c r="C2" s="2335" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="2116" t="s">
+      <c r="D2" s="2336" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="2117" t="s">
+      <c r="E2" s="2337" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2118" t="s">
+      <c r="A3" s="2338" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2119" t="s">
+      <c r="B3" s="2339" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="2120" t="s">
+      <c r="C3" s="2340" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="2121" t="s">
+      <c r="D3" s="2341" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="2122" t="s">
+      <c r="E3" s="2342" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2123" t="s">
+      <c r="A4" s="2343" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="2124" t="s">
+      <c r="B4" s="2344" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="2125" t="s">
+      <c r="C4" s="2345" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="2126" t="s">
+      <c r="D4" s="2346" t="s">
         <v>40</v>
       </c>
-      <c r="E4" s="2127" t="s">
+      <c r="E4" s="2347" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2128" t="s">
+      <c r="A5" s="2348" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="2129" t="s">
+      <c r="B5" s="2349" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="2130" t="s">
+      <c r="C5" s="2350" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="2131" t="s">
+      <c r="D5" s="2351" t="s">
         <v>44</v>
       </c>
-      <c r="E5" s="2132" t="s">
+      <c r="E5" s="2352" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2133" t="s">
+      <c r="A6" s="2353" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="2134" t="s">
+      <c r="B6" s="2354" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="2135" t="s">
+      <c r="C6" s="2355" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="2136" t="s">
+      <c r="D6" s="2356" t="s">
         <v>41</v>
       </c>
-      <c r="E6" s="2137" t="s">
+      <c r="E6" s="2357" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2138" t="s">
+      <c r="A7" s="2358" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="2139" t="s">
+      <c r="B7" s="2359" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="2140" t="s">
+      <c r="C7" s="2360" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="2141" t="s">
+      <c r="D7" s="2361" t="s">
         <v>42</v>
       </c>
-      <c r="E7" s="2142" t="s">
+      <c r="E7" s="2362" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2143" t="s">
+      <c r="A8" s="2363" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="2144" t="s">
+      <c r="B8" s="2364" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="2145" t="s">
+      <c r="C8" s="2365" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="2146" t="s">
+      <c r="D8" s="2366" t="s">
         <v>43</v>
       </c>
-      <c r="E8" s="2147" t="s">
+      <c r="E8" s="2367" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2148" t="s">
+      <c r="A9" s="2368" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="2149" t="s">
+      <c r="B9" s="2369" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="2150" t="s">
+      <c r="C9" s="2370" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="2151" t="s">
+      <c r="D9" s="2371" t="s">
         <v>1</v>
       </c>
-      <c r="E9" s="2152" t="s">
+      <c r="E9" s="2372" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2153" t="s">
+      <c r="A10" s="2373" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="2154" t="s">
+      <c r="B10" s="2374" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="2155" t="s">
+      <c r="C10" s="2375" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="2156" t="s">
+      <c r="D10" s="2376" t="s">
         <v>1</v>
       </c>
-      <c r="E10" s="2157" t="s">
+      <c r="E10" s="2377" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2158" t="s">
+      <c r="A11" s="2378" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="2159" t="s">
+      <c r="B11" s="2379" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="2160" t="s">
+      <c r="C11" s="2380" t="s">
         <v>37</v>
       </c>
-      <c r="D11" s="2161" t="s">
+      <c r="D11" s="2381" t="s">
         <v>1</v>
       </c>
-      <c r="E11" s="2162" t="s">
+      <c r="E11" s="2382" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2163" t="s">
+      <c r="A12" s="2383" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="2164" t="s">
+      <c r="B12" s="2384" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="2165" t="s">
+      <c r="C12" s="2385" t="s">
         <v>38</v>
       </c>
-      <c r="D12" s="2166" t="s">
+      <c r="D12" s="2386" t="s">
         <v>1</v>
       </c>
-      <c r="E12" s="2167" t="s">
+      <c r="E12" s="2387" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2168" t="s">
+      <c r="A13" s="2388" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="2169" t="s">
+      <c r="B13" s="2389" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="2170" t="s">
+      <c r="C13" s="2390" t="s">
         <v>45</v>
       </c>
-      <c r="D13" s="2171" t="s">
+      <c r="D13" s="2391" t="s">
         <v>1</v>
       </c>
-      <c r="E13" s="2172" t="s">
+      <c r="E13" s="2392" t="s">
         <v>1</v>
       </c>
     </row>
